--- a/frontend/public/templates/Items_Per_Task_Template.xlsx
+++ b/frontend/public/templates/Items_Per_Task_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\productivity_report\frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A35E7B3-9DD1-40CD-A1FC-BDBEBA2252F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF9989B-670D-4E01-AA12-B62DFAFC1C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-4740" windowWidth="29040" windowHeight="15720" xr2:uid="{913B4972-2756-447A-8FAA-904A73B41D83}"/>
   </bookViews>
@@ -38,11 +38,22 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -71,14 +82,34 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -411,8 +442,13 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="1" s="1" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <conditionalFormatting sqref="A1:XFD1">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>A1&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>